--- a/Interview Guide/React Js/Road Map.xlsx
+++ b/Interview Guide/React Js/Road Map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2081126\aem_practice\My Tectra AEM Git\My-Tectra-AEM-Tutorials-Practice\Interview Guide\React Js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A28391-FBBB-49B4-9CE9-0A10C8C8ADAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FECAF9A-93E9-43C7-87C2-48B3B7568826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -931,13 +931,13 @@
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
